--- a/artfynd/A 40482-2021 artfynd.xlsx
+++ b/artfynd/A 40482-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128360723</v>
       </c>
       <c r="B2" t="n">
-        <v>57334</v>
+        <v>57338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128359563</v>
       </c>
       <c r="B3" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128360779</v>
       </c>
       <c r="B4" t="n">
-        <v>56879</v>
+        <v>56883</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40482-2021 artfynd.xlsx
+++ b/artfynd/A 40482-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128360723</v>
       </c>
       <c r="B2" t="n">
-        <v>57338</v>
+        <v>57365</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128359563</v>
       </c>
       <c r="B3" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128360779</v>
       </c>
       <c r="B4" t="n">
-        <v>56883</v>
+        <v>56910</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,6 +993,2253 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128827571</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57876</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>536106</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6983996</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128825631</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57716</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>536307</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6983941</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128826049</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80221</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>536178</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6983840</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128824312</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57876</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>536282</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6983998</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128826022</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80221</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>536178</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6983822</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128826263</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57716</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>536215</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6983790</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128827725</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57716</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>536141</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6984011</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128827218</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80221</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>536125</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6983800</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128826667</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57716</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>536209</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6983785</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128826828</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57716</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>536179</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6983752</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128826455</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57876</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>536225</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6983790</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128826101</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57716</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>536189</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6983813</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128825959</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80221</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>536251</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6983900</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128826139</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80221</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>536203</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6983808</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128826203</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57716</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>536194</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6983796</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128825735</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57716</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>536298</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6983957</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128827111</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80249</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>536165</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6983788</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128827232</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57876</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>536125</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6983800</v>
+      </c>
+      <c r="S22" t="n">
+        <v>30</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128826031</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80221</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>536179</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6983823</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128826861</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80221</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>536179</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6983752</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128827644</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57716</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>536131</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6983999</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40482-2021 artfynd.xlsx
+++ b/artfynd/A 40482-2021 artfynd.xlsx
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128824312</v>
+        <v>128826263</v>
       </c>
       <c r="B8" t="n">
-        <v>57876</v>
+        <v>57716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,13 +1352,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536282</v>
+        <v>536215</v>
       </c>
       <c r="R8" t="n">
-        <v>6983998</v>
+        <v>6983790</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128826022</v>
+        <v>128827725</v>
       </c>
       <c r="B9" t="n">
-        <v>80221</v>
+        <v>57716</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536178</v>
+        <v>536141</v>
       </c>
       <c r="R9" t="n">
-        <v>6983822</v>
+        <v>6984011</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128826263</v>
+        <v>128824312</v>
       </c>
       <c r="B10" t="n">
-        <v>57716</v>
+        <v>57876</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,13 +1566,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536215</v>
+        <v>536282</v>
       </c>
       <c r="R10" t="n">
-        <v>6983790</v>
+        <v>6983998</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128827725</v>
+        <v>128826022</v>
       </c>
       <c r="B11" t="n">
-        <v>57716</v>
+        <v>80221</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536141</v>
+        <v>536178</v>
       </c>
       <c r="R11" t="n">
-        <v>6984011</v>
+        <v>6983822</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128826667</v>
+        <v>128826455</v>
       </c>
       <c r="B13" t="n">
-        <v>57716</v>
+        <v>57876</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,13 +1887,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536209</v>
+        <v>536225</v>
       </c>
       <c r="R13" t="n">
-        <v>6983785</v>
+        <v>6983790</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,7 +1959,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128826828</v>
+        <v>128826667</v>
       </c>
       <c r="B14" t="n">
         <v>57716</v>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536179</v>
+        <v>536209</v>
       </c>
       <c r="R14" t="n">
-        <v>6983752</v>
+        <v>6983785</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128826455</v>
+        <v>128826828</v>
       </c>
       <c r="B15" t="n">
-        <v>57876</v>
+        <v>57716</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,13 +2101,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>536225</v>
+        <v>536179</v>
       </c>
       <c r="R15" t="n">
-        <v>6983790</v>
+        <v>6983752</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2280,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128825959</v>
+        <v>128826203</v>
       </c>
       <c r="B17" t="n">
-        <v>80221</v>
+        <v>57716</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536251</v>
+        <v>536194</v>
       </c>
       <c r="R17" t="n">
-        <v>6983900</v>
+        <v>6983796</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2494,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128826203</v>
+        <v>128825959</v>
       </c>
       <c r="B19" t="n">
-        <v>57716</v>
+        <v>80221</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2505,21 +2505,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536194</v>
+        <v>536251</v>
       </c>
       <c r="R19" t="n">
-        <v>6983796</v>
+        <v>6983900</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2922,7 +2922,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128826031</v>
+        <v>128826861</v>
       </c>
       <c r="B23" t="n">
         <v>80221</v>
@@ -2960,7 +2960,7 @@
         <v>536179</v>
       </c>
       <c r="R23" t="n">
-        <v>6983823</v>
+        <v>6983752</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,7 +3029,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128826861</v>
+        <v>128826031</v>
       </c>
       <c r="B24" t="n">
         <v>80221</v>
@@ -3067,7 +3067,7 @@
         <v>536179</v>
       </c>
       <c r="R24" t="n">
-        <v>6983752</v>
+        <v>6983823</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 40482-2021 artfynd.xlsx
+++ b/artfynd/A 40482-2021 artfynd.xlsx
@@ -1213,7 +1213,7 @@
         <v>128826049</v>
       </c>
       <c r="B7" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128826263</v>
+        <v>128826022</v>
       </c>
       <c r="B8" t="n">
-        <v>57716</v>
+        <v>80225</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536215</v>
+        <v>536178</v>
       </c>
       <c r="R8" t="n">
-        <v>6983790</v>
+        <v>6983822</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128824312</v>
+        <v>128826263</v>
       </c>
       <c r="B10" t="n">
-        <v>57876</v>
+        <v>57716</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,13 +1566,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536282</v>
+        <v>536215</v>
       </c>
       <c r="R10" t="n">
-        <v>6983998</v>
+        <v>6983790</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128826022</v>
+        <v>128824312</v>
       </c>
       <c r="B11" t="n">
-        <v>80221</v>
+        <v>57876</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536178</v>
+        <v>536282</v>
       </c>
       <c r="R11" t="n">
-        <v>6983822</v>
+        <v>6983998</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1748,7 +1748,7 @@
         <v>128827218</v>
       </c>
       <c r="B12" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128826203</v>
+        <v>128826139</v>
       </c>
       <c r="B17" t="n">
-        <v>57716</v>
+        <v>80225</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536194</v>
+        <v>536203</v>
       </c>
       <c r="R17" t="n">
-        <v>6983796</v>
+        <v>6983808</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128826139</v>
+        <v>128825959</v>
       </c>
       <c r="B18" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536203</v>
+        <v>536251</v>
       </c>
       <c r="R18" t="n">
-        <v>6983808</v>
+        <v>6983900</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128825959</v>
+        <v>128826203</v>
       </c>
       <c r="B19" t="n">
-        <v>80221</v>
+        <v>57716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2505,21 +2505,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536251</v>
+        <v>536194</v>
       </c>
       <c r="R19" t="n">
-        <v>6983900</v>
+        <v>6983796</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2711,7 +2711,7 @@
         <v>128827111</v>
       </c>
       <c r="B21" t="n">
-        <v>80249</v>
+        <v>80253</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>128826861</v>
       </c>
       <c r="B23" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>128826031</v>
       </c>
       <c r="B24" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 40482-2021 artfynd.xlsx
+++ b/artfynd/A 40482-2021 artfynd.xlsx
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128826455</v>
+        <v>128826667</v>
       </c>
       <c r="B13" t="n">
-        <v>57876</v>
+        <v>57716</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,13 +1887,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536225</v>
+        <v>536209</v>
       </c>
       <c r="R13" t="n">
-        <v>6983790</v>
+        <v>6983785</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,7 +1959,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128826667</v>
+        <v>128826828</v>
       </c>
       <c r="B14" t="n">
         <v>57716</v>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536209</v>
+        <v>536179</v>
       </c>
       <c r="R14" t="n">
-        <v>6983785</v>
+        <v>6983752</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128826828</v>
+        <v>128826455</v>
       </c>
       <c r="B15" t="n">
-        <v>57716</v>
+        <v>57876</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,13 +2101,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>536179</v>
+        <v>536225</v>
       </c>
       <c r="R15" t="n">
-        <v>6983752</v>
+        <v>6983790</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2280,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128826139</v>
+        <v>128826203</v>
       </c>
       <c r="B17" t="n">
-        <v>80225</v>
+        <v>57716</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536203</v>
+        <v>536194</v>
       </c>
       <c r="R17" t="n">
-        <v>6983808</v>
+        <v>6983796</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,7 +2387,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128825959</v>
+        <v>128826139</v>
       </c>
       <c r="B18" t="n">
         <v>80225</v>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536251</v>
+        <v>536203</v>
       </c>
       <c r="R18" t="n">
-        <v>6983900</v>
+        <v>6983808</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128826203</v>
+        <v>128825959</v>
       </c>
       <c r="B19" t="n">
-        <v>57716</v>
+        <v>80225</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2505,21 +2505,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536194</v>
+        <v>536251</v>
       </c>
       <c r="R19" t="n">
-        <v>6983796</v>
+        <v>6983900</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 40482-2021 artfynd.xlsx
+++ b/artfynd/A 40482-2021 artfynd.xlsx
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128826022</v>
+        <v>128827725</v>
       </c>
       <c r="B8" t="n">
-        <v>80225</v>
+        <v>57716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536178</v>
+        <v>536141</v>
       </c>
       <c r="R8" t="n">
-        <v>6983822</v>
+        <v>6984011</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128827725</v>
+        <v>128826022</v>
       </c>
       <c r="B9" t="n">
-        <v>57716</v>
+        <v>80225</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536141</v>
+        <v>536178</v>
       </c>
       <c r="R9" t="n">
-        <v>6984011</v>
+        <v>6983822</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2280,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128826203</v>
+        <v>128826139</v>
       </c>
       <c r="B17" t="n">
-        <v>57716</v>
+        <v>80225</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536194</v>
+        <v>536203</v>
       </c>
       <c r="R17" t="n">
-        <v>6983796</v>
+        <v>6983808</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,7 +2387,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128826139</v>
+        <v>128825959</v>
       </c>
       <c r="B18" t="n">
         <v>80225</v>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536203</v>
+        <v>536251</v>
       </c>
       <c r="R18" t="n">
-        <v>6983808</v>
+        <v>6983900</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128825959</v>
+        <v>128826203</v>
       </c>
       <c r="B19" t="n">
-        <v>80225</v>
+        <v>57716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2505,21 +2505,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536251</v>
+        <v>536194</v>
       </c>
       <c r="R19" t="n">
-        <v>6983900</v>
+        <v>6983796</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 40482-2021 artfynd.xlsx
+++ b/artfynd/A 40482-2021 artfynd.xlsx
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128827725</v>
+        <v>128826022</v>
       </c>
       <c r="B8" t="n">
-        <v>57716</v>
+        <v>80225</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536141</v>
+        <v>536178</v>
       </c>
       <c r="R8" t="n">
-        <v>6984011</v>
+        <v>6983822</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128826022</v>
+        <v>128826263</v>
       </c>
       <c r="B9" t="n">
-        <v>80225</v>
+        <v>57716</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536178</v>
+        <v>536215</v>
       </c>
       <c r="R9" t="n">
-        <v>6983822</v>
+        <v>6983790</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128826263</v>
+        <v>128827725</v>
       </c>
       <c r="B10" t="n">
         <v>57716</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536215</v>
+        <v>536141</v>
       </c>
       <c r="R10" t="n">
-        <v>6983790</v>
+        <v>6984011</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 40482-2021 artfynd.xlsx
+++ b/artfynd/A 40482-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128360723</v>
       </c>
       <c r="B2" t="n">
-        <v>57365</v>
+        <v>57369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128359563</v>
       </c>
       <c r="B3" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128360779</v>
       </c>
       <c r="B4" t="n">
-        <v>56910</v>
+        <v>56913</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128827571</v>
       </c>
       <c r="B5" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128825631</v>
       </c>
       <c r="B6" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128826049</v>
       </c>
       <c r="B7" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>128826022</v>
       </c>
       <c r="B8" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>128826263</v>
       </c>
       <c r="B9" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>128827725</v>
       </c>
       <c r="B10" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>128824312</v>
       </c>
       <c r="B11" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>128827218</v>
       </c>
       <c r="B12" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>128826667</v>
       </c>
       <c r="B13" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>128826828</v>
       </c>
       <c r="B14" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>128826455</v>
       </c>
       <c r="B15" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>128826101</v>
       </c>
       <c r="B16" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128826139</v>
+        <v>128826203</v>
       </c>
       <c r="B17" t="n">
-        <v>80225</v>
+        <v>57720</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536203</v>
+        <v>536194</v>
       </c>
       <c r="R17" t="n">
-        <v>6983808</v>
+        <v>6983796</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128825959</v>
+        <v>128826139</v>
       </c>
       <c r="B18" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536251</v>
+        <v>536203</v>
       </c>
       <c r="R18" t="n">
-        <v>6983900</v>
+        <v>6983808</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128826203</v>
+        <v>128825959</v>
       </c>
       <c r="B19" t="n">
-        <v>57716</v>
+        <v>80229</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2505,21 +2505,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536194</v>
+        <v>536251</v>
       </c>
       <c r="R19" t="n">
-        <v>6983796</v>
+        <v>6983900</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2604,7 +2604,7 @@
         <v>128825735</v>
       </c>
       <c r="B20" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2708,32 +2708,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128827111</v>
+        <v>128827232</v>
       </c>
       <c r="B21" t="n">
-        <v>80253</v>
+        <v>57880</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,13 +2743,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>536165</v>
+        <v>536125</v>
       </c>
       <c r="R21" t="n">
-        <v>6983788</v>
+        <v>6983800</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,32 +2815,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128827232</v>
+        <v>128827111</v>
       </c>
       <c r="B22" t="n">
-        <v>57876</v>
+        <v>80257</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,13 +2850,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>536125</v>
+        <v>536165</v>
       </c>
       <c r="R22" t="n">
-        <v>6983800</v>
+        <v>6983788</v>
       </c>
       <c r="S22" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2925,7 +2925,7 @@
         <v>128826861</v>
       </c>
       <c r="B23" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>128826031</v>
       </c>
       <c r="B24" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>128827644</v>
       </c>
       <c r="B25" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 40482-2021 artfynd.xlsx
+++ b/artfynd/A 40482-2021 artfynd.xlsx
@@ -1852,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128826667</v>
+        <v>128826828</v>
       </c>
       <c r="B13" t="n">
         <v>57720</v>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536209</v>
+        <v>536179</v>
       </c>
       <c r="R13" t="n">
-        <v>6983785</v>
+        <v>6983752</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,7 +1959,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128826828</v>
+        <v>128826667</v>
       </c>
       <c r="B14" t="n">
         <v>57720</v>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536179</v>
+        <v>536209</v>
       </c>
       <c r="R14" t="n">
-        <v>6983752</v>
+        <v>6983785</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2280,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128826203</v>
+        <v>128826139</v>
       </c>
       <c r="B17" t="n">
-        <v>57720</v>
+        <v>80229</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536194</v>
+        <v>536203</v>
       </c>
       <c r="R17" t="n">
-        <v>6983796</v>
+        <v>6983808</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,7 +2387,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128826139</v>
+        <v>128825959</v>
       </c>
       <c r="B18" t="n">
         <v>80229</v>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536203</v>
+        <v>536251</v>
       </c>
       <c r="R18" t="n">
-        <v>6983808</v>
+        <v>6983900</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128825959</v>
+        <v>128826203</v>
       </c>
       <c r="B19" t="n">
-        <v>80229</v>
+        <v>57720</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2505,21 +2505,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536251</v>
+        <v>536194</v>
       </c>
       <c r="R19" t="n">
-        <v>6983900</v>
+        <v>6983796</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2922,7 +2922,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128826861</v>
+        <v>128826031</v>
       </c>
       <c r="B23" t="n">
         <v>80229</v>
@@ -2960,7 +2960,7 @@
         <v>536179</v>
       </c>
       <c r="R23" t="n">
-        <v>6983752</v>
+        <v>6983823</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,7 +3029,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128826031</v>
+        <v>128826861</v>
       </c>
       <c r="B24" t="n">
         <v>80229</v>
@@ -3067,7 +3067,7 @@
         <v>536179</v>
       </c>
       <c r="R24" t="n">
-        <v>6983823</v>
+        <v>6983752</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 40482-2021 artfynd.xlsx
+++ b/artfynd/A 40482-2021 artfynd.xlsx
@@ -1852,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128826828</v>
+        <v>128826667</v>
       </c>
       <c r="B13" t="n">
         <v>57720</v>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536179</v>
+        <v>536209</v>
       </c>
       <c r="R13" t="n">
-        <v>6983752</v>
+        <v>6983785</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,7 +1959,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128826667</v>
+        <v>128826828</v>
       </c>
       <c r="B14" t="n">
         <v>57720</v>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536209</v>
+        <v>536179</v>
       </c>
       <c r="R14" t="n">
-        <v>6983785</v>
+        <v>6983752</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2708,32 +2708,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128827232</v>
+        <v>128827111</v>
       </c>
       <c r="B21" t="n">
-        <v>57880</v>
+        <v>80257</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,13 +2743,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>536125</v>
+        <v>536165</v>
       </c>
       <c r="R21" t="n">
-        <v>6983800</v>
+        <v>6983788</v>
       </c>
       <c r="S21" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,32 +2815,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128827111</v>
+        <v>128827232</v>
       </c>
       <c r="B22" t="n">
-        <v>80257</v>
+        <v>57880</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,13 +2850,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>536165</v>
+        <v>536125</v>
       </c>
       <c r="R22" t="n">
-        <v>6983788</v>
+        <v>6983800</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,7 +2922,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128826031</v>
+        <v>128826861</v>
       </c>
       <c r="B23" t="n">
         <v>80229</v>
@@ -2960,7 +2960,7 @@
         <v>536179</v>
       </c>
       <c r="R23" t="n">
-        <v>6983823</v>
+        <v>6983752</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,7 +3029,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128826861</v>
+        <v>128826031</v>
       </c>
       <c r="B24" t="n">
         <v>80229</v>
@@ -3067,7 +3067,7 @@
         <v>536179</v>
       </c>
       <c r="R24" t="n">
-        <v>6983752</v>
+        <v>6983823</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 40482-2021 artfynd.xlsx
+++ b/artfynd/A 40482-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128360723</v>
       </c>
       <c r="B2" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128359563</v>
       </c>
       <c r="B3" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128360779</v>
       </c>
       <c r="B4" t="n">
-        <v>56913</v>
+        <v>56916</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128827571</v>
       </c>
       <c r="B5" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128825631</v>
       </c>
       <c r="B6" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128826049</v>
       </c>
       <c r="B7" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128826022</v>
+        <v>128827725</v>
       </c>
       <c r="B8" t="n">
-        <v>80229</v>
+        <v>57723</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536178</v>
+        <v>536141</v>
       </c>
       <c r="R8" t="n">
-        <v>6983822</v>
+        <v>6984011</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,7 +1427,7 @@
         <v>128826263</v>
       </c>
       <c r="B9" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128827725</v>
+        <v>128826022</v>
       </c>
       <c r="B10" t="n">
-        <v>57720</v>
+        <v>80134</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536141</v>
+        <v>536178</v>
       </c>
       <c r="R10" t="n">
-        <v>6984011</v>
+        <v>6983822</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,7 +1641,7 @@
         <v>128824312</v>
       </c>
       <c r="B11" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>128827218</v>
       </c>
       <c r="B12" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128826667</v>
+        <v>128826455</v>
       </c>
       <c r="B13" t="n">
-        <v>57720</v>
+        <v>57883</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,13 +1887,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536209</v>
+        <v>536225</v>
       </c>
       <c r="R13" t="n">
-        <v>6983785</v>
+        <v>6983790</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128826828</v>
+        <v>128826667</v>
       </c>
       <c r="B14" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536179</v>
+        <v>536209</v>
       </c>
       <c r="R14" t="n">
-        <v>6983752</v>
+        <v>6983785</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128826455</v>
+        <v>128826828</v>
       </c>
       <c r="B15" t="n">
-        <v>57880</v>
+        <v>57723</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,13 +2101,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>536225</v>
+        <v>536179</v>
       </c>
       <c r="R15" t="n">
-        <v>6983790</v>
+        <v>6983752</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2176,7 +2176,7 @@
         <v>128826101</v>
       </c>
       <c r="B16" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128826139</v>
+        <v>128826203</v>
       </c>
       <c r="B17" t="n">
-        <v>80229</v>
+        <v>57723</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536203</v>
+        <v>536194</v>
       </c>
       <c r="R17" t="n">
-        <v>6983808</v>
+        <v>6983796</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128825959</v>
+        <v>128826139</v>
       </c>
       <c r="B18" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536251</v>
+        <v>536203</v>
       </c>
       <c r="R18" t="n">
-        <v>6983900</v>
+        <v>6983808</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128826203</v>
+        <v>128825959</v>
       </c>
       <c r="B19" t="n">
-        <v>57720</v>
+        <v>80134</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2505,21 +2505,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536194</v>
+        <v>536251</v>
       </c>
       <c r="R19" t="n">
-        <v>6983796</v>
+        <v>6983900</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2604,7 +2604,7 @@
         <v>128825735</v>
       </c>
       <c r="B20" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2708,32 +2708,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128827111</v>
+        <v>128827232</v>
       </c>
       <c r="B21" t="n">
-        <v>80257</v>
+        <v>57883</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,13 +2743,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>536165</v>
+        <v>536125</v>
       </c>
       <c r="R21" t="n">
-        <v>6983788</v>
+        <v>6983800</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,32 +2815,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128827232</v>
+        <v>128827111</v>
       </c>
       <c r="B22" t="n">
-        <v>57880</v>
+        <v>80162</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,13 +2850,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>536125</v>
+        <v>536165</v>
       </c>
       <c r="R22" t="n">
-        <v>6983800</v>
+        <v>6983788</v>
       </c>
       <c r="S22" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2925,7 +2925,7 @@
         <v>128826861</v>
       </c>
       <c r="B23" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>128826031</v>
       </c>
       <c r="B24" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>128827644</v>
       </c>
       <c r="B25" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 40482-2021 artfynd.xlsx
+++ b/artfynd/A 40482-2021 artfynd.xlsx
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128826667</v>
+        <v>128826455</v>
       </c>
       <c r="B13" t="n">
-        <v>57723</v>
+        <v>57883</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,13 +1887,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536209</v>
+        <v>536225</v>
       </c>
       <c r="R13" t="n">
-        <v>6983785</v>
+        <v>6983790</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128826455</v>
+        <v>128826101</v>
       </c>
       <c r="B15" t="n">
-        <v>57883</v>
+        <v>57723</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,13 +2101,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>536225</v>
+        <v>536189</v>
       </c>
       <c r="R15" t="n">
-        <v>6983790</v>
+        <v>6983813</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128826101</v>
+        <v>128826139</v>
       </c>
       <c r="B16" t="n">
-        <v>57723</v>
+        <v>80139</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536189</v>
+        <v>536203</v>
       </c>
       <c r="R16" t="n">
-        <v>6983813</v>
+        <v>6983808</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,7 +2280,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128826139</v>
+        <v>128825959</v>
       </c>
       <c r="B17" t="n">
         <v>80139</v>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536203</v>
+        <v>536251</v>
       </c>
       <c r="R17" t="n">
-        <v>6983808</v>
+        <v>6983900</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128825959</v>
+        <v>128826203</v>
       </c>
       <c r="B18" t="n">
-        <v>80139</v>
+        <v>57723</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2398,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536251</v>
+        <v>536194</v>
       </c>
       <c r="R18" t="n">
-        <v>6983900</v>
+        <v>6983796</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,7 +2494,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128826203</v>
+        <v>128825735</v>
       </c>
       <c r="B19" t="n">
         <v>57723</v>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536194</v>
+        <v>536298</v>
       </c>
       <c r="R19" t="n">
-        <v>6983796</v>
+        <v>6983957</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2601,32 +2601,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128825735</v>
+        <v>128827111</v>
       </c>
       <c r="B20" t="n">
-        <v>57723</v>
+        <v>80167</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>536298</v>
+        <v>536165</v>
       </c>
       <c r="R20" t="n">
-        <v>6983957</v>
+        <v>6983788</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,32 +2708,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128827111</v>
+        <v>128827232</v>
       </c>
       <c r="B21" t="n">
-        <v>80167</v>
+        <v>57883</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,13 +2743,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>536165</v>
+        <v>536125</v>
       </c>
       <c r="R21" t="n">
-        <v>6983788</v>
+        <v>6983800</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128827232</v>
+        <v>128826861</v>
       </c>
       <c r="B22" t="n">
-        <v>57883</v>
+        <v>80139</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2826,21 +2826,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,13 +2850,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>536125</v>
+        <v>536179</v>
       </c>
       <c r="R22" t="n">
-        <v>6983800</v>
+        <v>6983752</v>
       </c>
       <c r="S22" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,7 +2922,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128826861</v>
+        <v>128826031</v>
       </c>
       <c r="B23" t="n">
         <v>80139</v>
@@ -2960,7 +2960,7 @@
         <v>536179</v>
       </c>
       <c r="R23" t="n">
-        <v>6983752</v>
+        <v>6983823</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128826031</v>
+        <v>128827644</v>
       </c>
       <c r="B24" t="n">
-        <v>80139</v>
+        <v>57723</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,21 +3040,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3064,13 +3064,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>536179</v>
+        <v>536131</v>
       </c>
       <c r="R24" t="n">
-        <v>6983823</v>
+        <v>6983999</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3136,7 +3136,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128827644</v>
+        <v>128826667</v>
       </c>
       <c r="B25" t="n">
         <v>57723</v>
@@ -3165,19 +3165,23 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kroktjärnen, Kroktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>536131</v>
+        <v>536209</v>
       </c>
       <c r="R25" t="n">
-        <v>6983999</v>
+        <v>6983785</v>
       </c>
       <c r="S25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3206,7 +3210,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3216,7 +3220,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 40482-2021 artfynd.xlsx
+++ b/artfynd/A 40482-2021 artfynd.xlsx
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128826263</v>
+        <v>128824312</v>
       </c>
       <c r="B9" t="n">
-        <v>57723</v>
+        <v>57883</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,13 +1459,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536215</v>
+        <v>536282</v>
       </c>
       <c r="R9" t="n">
-        <v>6983790</v>
+        <v>6983998</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128824312</v>
+        <v>128826263</v>
       </c>
       <c r="B11" t="n">
-        <v>57883</v>
+        <v>57723</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536282</v>
+        <v>536215</v>
       </c>
       <c r="R11" t="n">
-        <v>6983998</v>
+        <v>6983790</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128826455</v>
+        <v>128826828</v>
       </c>
       <c r="B13" t="n">
-        <v>57883</v>
+        <v>57723</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,13 +1887,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536225</v>
+        <v>536179</v>
       </c>
       <c r="R13" t="n">
-        <v>6983790</v>
+        <v>6983752</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128826828</v>
+        <v>128826455</v>
       </c>
       <c r="B14" t="n">
-        <v>57723</v>
+        <v>57883</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536179</v>
+        <v>536225</v>
       </c>
       <c r="R14" t="n">
-        <v>6983752</v>
+        <v>6983790</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 40482-2021 artfynd.xlsx
+++ b/artfynd/A 40482-2021 artfynd.xlsx
@@ -1213,7 +1213,7 @@
         <v>128826049</v>
       </c>
       <c r="B7" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128826022</v>
+        <v>128824312</v>
       </c>
       <c r="B8" t="n">
-        <v>80139</v>
+        <v>57883</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,13 +1352,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536178</v>
+        <v>536282</v>
       </c>
       <c r="R8" t="n">
-        <v>6983822</v>
+        <v>6983998</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128824312</v>
+        <v>128826022</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
+        <v>80140</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,13 +1459,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536282</v>
+        <v>536178</v>
       </c>
       <c r="R9" t="n">
-        <v>6983998</v>
+        <v>6983822</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1748,7 +1748,7 @@
         <v>128827218</v>
       </c>
       <c r="B12" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128826828</v>
+        <v>128826455</v>
       </c>
       <c r="B13" t="n">
-        <v>57723</v>
+        <v>57883</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,13 +1887,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536179</v>
+        <v>536225</v>
       </c>
       <c r="R13" t="n">
-        <v>6983752</v>
+        <v>6983790</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128826455</v>
+        <v>128826828</v>
       </c>
       <c r="B14" t="n">
-        <v>57883</v>
+        <v>57723</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536225</v>
+        <v>536179</v>
       </c>
       <c r="R14" t="n">
-        <v>6983790</v>
+        <v>6983752</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2176,7 +2176,7 @@
         <v>128826139</v>
       </c>
       <c r="B16" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>128825959</v>
       </c>
       <c r="B17" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>128827111</v>
       </c>
       <c r="B20" t="n">
-        <v>80167</v>
+        <v>80168</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>128826861</v>
       </c>
       <c r="B22" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>128826031</v>
       </c>
       <c r="B23" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 40482-2021 artfynd.xlsx
+++ b/artfynd/A 40482-2021 artfynd.xlsx
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128824312</v>
+        <v>128827725</v>
       </c>
       <c r="B8" t="n">
-        <v>57883</v>
+        <v>57723</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,13 +1352,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536282</v>
+        <v>536141</v>
       </c>
       <c r="R8" t="n">
-        <v>6983998</v>
+        <v>6984011</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128826022</v>
+        <v>128826263</v>
       </c>
       <c r="B9" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536178</v>
+        <v>536215</v>
       </c>
       <c r="R9" t="n">
-        <v>6983822</v>
+        <v>6983790</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128827725</v>
+        <v>128826022</v>
       </c>
       <c r="B10" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536141</v>
+        <v>536178</v>
       </c>
       <c r="R10" t="n">
-        <v>6984011</v>
+        <v>6983822</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128826263</v>
+        <v>128824312</v>
       </c>
       <c r="B11" t="n">
-        <v>57723</v>
+        <v>57883</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536215</v>
+        <v>536282</v>
       </c>
       <c r="R11" t="n">
-        <v>6983790</v>
+        <v>6983998</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128826455</v>
+        <v>128826828</v>
       </c>
       <c r="B13" t="n">
-        <v>57883</v>
+        <v>57723</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,13 +1887,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536225</v>
+        <v>536179</v>
       </c>
       <c r="R13" t="n">
-        <v>6983790</v>
+        <v>6983752</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128826828</v>
+        <v>128826455</v>
       </c>
       <c r="B14" t="n">
-        <v>57723</v>
+        <v>57883</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536179</v>
+        <v>536225</v>
       </c>
       <c r="R14" t="n">
-        <v>6983752</v>
+        <v>6983790</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 40482-2021 artfynd.xlsx
+++ b/artfynd/A 40482-2021 artfynd.xlsx
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128827725</v>
+        <v>128826022</v>
       </c>
       <c r="B8" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536141</v>
+        <v>536178</v>
       </c>
       <c r="R8" t="n">
-        <v>6984011</v>
+        <v>6983822</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128826263</v>
+        <v>128827725</v>
       </c>
       <c r="B9" t="n">
         <v>57723</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536215</v>
+        <v>536141</v>
       </c>
       <c r="R9" t="n">
-        <v>6983790</v>
+        <v>6984011</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128826022</v>
+        <v>128826263</v>
       </c>
       <c r="B10" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536178</v>
+        <v>536215</v>
       </c>
       <c r="R10" t="n">
-        <v>6983822</v>
+        <v>6983790</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 40482-2021 artfynd.xlsx
+++ b/artfynd/A 40482-2021 artfynd.xlsx
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128827725</v>
+        <v>128826263</v>
       </c>
       <c r="B9" t="n">
         <v>57723</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536141</v>
+        <v>536215</v>
       </c>
       <c r="R9" t="n">
-        <v>6984011</v>
+        <v>6983790</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128826263</v>
+        <v>128827725</v>
       </c>
       <c r="B10" t="n">
         <v>57723</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536215</v>
+        <v>536141</v>
       </c>
       <c r="R10" t="n">
-        <v>6983790</v>
+        <v>6984011</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 40482-2021 artfynd.xlsx
+++ b/artfynd/A 40482-2021 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>128827571</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128825631</v>
       </c>
       <c r="B6" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128826049</v>
       </c>
       <c r="B7" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128826022</v>
+        <v>128824312</v>
       </c>
       <c r="B8" t="n">
-        <v>80140</v>
+        <v>57885</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,13 +1352,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536178</v>
+        <v>536282</v>
       </c>
       <c r="R8" t="n">
-        <v>6983822</v>
+        <v>6983998</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128826263</v>
+        <v>128826022</v>
       </c>
       <c r="B9" t="n">
-        <v>57723</v>
+        <v>80144</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536215</v>
+        <v>536178</v>
       </c>
       <c r="R9" t="n">
-        <v>6983790</v>
+        <v>6983822</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,7 +1534,7 @@
         <v>128827725</v>
       </c>
       <c r="B10" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128824312</v>
+        <v>128826263</v>
       </c>
       <c r="B11" t="n">
-        <v>57883</v>
+        <v>57725</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536282</v>
+        <v>536215</v>
       </c>
       <c r="R11" t="n">
-        <v>6983998</v>
+        <v>6983790</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1748,7 +1748,7 @@
         <v>128827218</v>
       </c>
       <c r="B12" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>128826828</v>
       </c>
       <c r="B13" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>128826455</v>
       </c>
       <c r="B14" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>128826101</v>
       </c>
       <c r="B15" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128826139</v>
+        <v>128826203</v>
       </c>
       <c r="B16" t="n">
-        <v>80140</v>
+        <v>57725</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536203</v>
+        <v>536194</v>
       </c>
       <c r="R16" t="n">
-        <v>6983808</v>
+        <v>6983796</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128825959</v>
+        <v>128826139</v>
       </c>
       <c r="B17" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536251</v>
+        <v>536203</v>
       </c>
       <c r="R17" t="n">
-        <v>6983900</v>
+        <v>6983808</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128826203</v>
+        <v>128825959</v>
       </c>
       <c r="B18" t="n">
-        <v>57723</v>
+        <v>80144</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2398,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536194</v>
+        <v>536251</v>
       </c>
       <c r="R18" t="n">
-        <v>6983796</v>
+        <v>6983900</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2497,7 +2497,7 @@
         <v>128825735</v>
       </c>
       <c r="B19" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>128827111</v>
       </c>
       <c r="B20" t="n">
-        <v>80168</v>
+        <v>80172</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>128827232</v>
       </c>
       <c r="B21" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2815,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128826861</v>
+        <v>128826031</v>
       </c>
       <c r="B22" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>536179</v>
       </c>
       <c r="R22" t="n">
-        <v>6983752</v>
+        <v>6983823</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,10 +2922,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128826031</v>
+        <v>128826861</v>
       </c>
       <c r="B23" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>536179</v>
       </c>
       <c r="R23" t="n">
-        <v>6983823</v>
+        <v>6983752</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3032,7 +3032,7 @@
         <v>128827644</v>
       </c>
       <c r="B24" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>128826667</v>
       </c>
       <c r="B25" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 40482-2021 artfynd.xlsx
+++ b/artfynd/A 40482-2021 artfynd.xlsx
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128824312</v>
+        <v>128826022</v>
       </c>
       <c r="B8" t="n">
-        <v>57885</v>
+        <v>80144</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,13 +1352,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536282</v>
+        <v>536178</v>
       </c>
       <c r="R8" t="n">
-        <v>6983998</v>
+        <v>6983822</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128826022</v>
+        <v>128824312</v>
       </c>
       <c r="B9" t="n">
-        <v>80144</v>
+        <v>57885</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,13 +1459,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536178</v>
+        <v>536282</v>
       </c>
       <c r="R9" t="n">
-        <v>6983822</v>
+        <v>6983998</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 40482-2021 artfynd.xlsx
+++ b/artfynd/A 40482-2021 artfynd.xlsx
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128826022</v>
+        <v>128826263</v>
       </c>
       <c r="B8" t="n">
-        <v>80144</v>
+        <v>57725</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536178</v>
+        <v>536215</v>
       </c>
       <c r="R8" t="n">
-        <v>6983822</v>
+        <v>6983790</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128824312</v>
+        <v>128827725</v>
       </c>
       <c r="B9" t="n">
-        <v>57885</v>
+        <v>57725</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,13 +1459,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536282</v>
+        <v>536141</v>
       </c>
       <c r="R9" t="n">
-        <v>6983998</v>
+        <v>6984011</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128827725</v>
+        <v>128826022</v>
       </c>
       <c r="B10" t="n">
-        <v>57725</v>
+        <v>80144</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536141</v>
+        <v>536178</v>
       </c>
       <c r="R10" t="n">
-        <v>6984011</v>
+        <v>6983822</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128826263</v>
+        <v>128824312</v>
       </c>
       <c r="B11" t="n">
-        <v>57725</v>
+        <v>57885</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536215</v>
+        <v>536282</v>
       </c>
       <c r="R11" t="n">
-        <v>6983790</v>
+        <v>6983998</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128826203</v>
+        <v>128826139</v>
       </c>
       <c r="B16" t="n">
-        <v>57725</v>
+        <v>80144</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536194</v>
+        <v>536203</v>
       </c>
       <c r="R16" t="n">
-        <v>6983796</v>
+        <v>6983808</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128826139</v>
+        <v>128826203</v>
       </c>
       <c r="B17" t="n">
-        <v>80144</v>
+        <v>57725</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536203</v>
+        <v>536194</v>
       </c>
       <c r="R17" t="n">
-        <v>6983808</v>
+        <v>6983796</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2601,32 +2601,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128827111</v>
+        <v>128827232</v>
       </c>
       <c r="B20" t="n">
-        <v>80172</v>
+        <v>57885</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,13 +2636,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>536165</v>
+        <v>536125</v>
       </c>
       <c r="R20" t="n">
-        <v>6983788</v>
+        <v>6983800</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,32 +2708,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128827232</v>
+        <v>128827111</v>
       </c>
       <c r="B21" t="n">
-        <v>57885</v>
+        <v>80172</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,13 +2743,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>536125</v>
+        <v>536165</v>
       </c>
       <c r="R21" t="n">
-        <v>6983800</v>
+        <v>6983788</v>
       </c>
       <c r="S21" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,7 +2815,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128826031</v>
+        <v>128826861</v>
       </c>
       <c r="B22" t="n">
         <v>80144</v>
@@ -2853,7 +2853,7 @@
         <v>536179</v>
       </c>
       <c r="R22" t="n">
-        <v>6983823</v>
+        <v>6983752</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,7 +2922,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128826861</v>
+        <v>128826031</v>
       </c>
       <c r="B23" t="n">
         <v>80144</v>
@@ -2960,7 +2960,7 @@
         <v>536179</v>
       </c>
       <c r="R23" t="n">
-        <v>6983752</v>
+        <v>6983823</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 40482-2021 artfynd.xlsx
+++ b/artfynd/A 40482-2021 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>128827571</v>
       </c>
       <c r="B5" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128825631</v>
       </c>
       <c r="B6" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128826049</v>
       </c>
       <c r="B7" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128826263</v>
+        <v>128827725</v>
       </c>
       <c r="B8" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536215</v>
+        <v>536141</v>
       </c>
       <c r="R8" t="n">
-        <v>6983790</v>
+        <v>6984011</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128827725</v>
+        <v>128826263</v>
       </c>
       <c r="B9" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536141</v>
+        <v>536215</v>
       </c>
       <c r="R9" t="n">
-        <v>6984011</v>
+        <v>6983790</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,7 +1534,7 @@
         <v>128826022</v>
       </c>
       <c r="B10" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>128824312</v>
       </c>
       <c r="B11" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>128827218</v>
       </c>
       <c r="B12" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>128826828</v>
       </c>
       <c r="B13" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>128826455</v>
       </c>
       <c r="B14" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>128826101</v>
       </c>
       <c r="B15" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>128826139</v>
       </c>
       <c r="B16" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128826203</v>
+        <v>128825959</v>
       </c>
       <c r="B17" t="n">
-        <v>57725</v>
+        <v>80146</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536194</v>
+        <v>536251</v>
       </c>
       <c r="R17" t="n">
-        <v>6983796</v>
+        <v>6983900</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128825959</v>
+        <v>128826203</v>
       </c>
       <c r="B18" t="n">
-        <v>80144</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2398,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536251</v>
+        <v>536194</v>
       </c>
       <c r="R18" t="n">
-        <v>6983900</v>
+        <v>6983796</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2497,7 +2497,7 @@
         <v>128825735</v>
       </c>
       <c r="B19" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,32 +2601,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128827232</v>
+        <v>128827111</v>
       </c>
       <c r="B20" t="n">
-        <v>57885</v>
+        <v>80174</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,13 +2636,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>536125</v>
+        <v>536165</v>
       </c>
       <c r="R20" t="n">
-        <v>6983800</v>
+        <v>6983788</v>
       </c>
       <c r="S20" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,32 +2708,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128827111</v>
+        <v>128827232</v>
       </c>
       <c r="B21" t="n">
-        <v>80172</v>
+        <v>57887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,13 +2743,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>536165</v>
+        <v>536125</v>
       </c>
       <c r="R21" t="n">
-        <v>6983788</v>
+        <v>6983800</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2818,7 +2818,7 @@
         <v>128826861</v>
       </c>
       <c r="B22" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>128826031</v>
       </c>
       <c r="B23" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>128827644</v>
       </c>
       <c r="B24" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>128826667</v>
       </c>
       <c r="B25" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 40482-2021 artfynd.xlsx
+++ b/artfynd/A 40482-2021 artfynd.xlsx
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128827725</v>
+        <v>128826263</v>
       </c>
       <c r="B8" t="n">
         <v>57727</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536141</v>
+        <v>536215</v>
       </c>
       <c r="R8" t="n">
-        <v>6984011</v>
+        <v>6983790</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128826263</v>
+        <v>128827725</v>
       </c>
       <c r="B9" t="n">
         <v>57727</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536215</v>
+        <v>536141</v>
       </c>
       <c r="R9" t="n">
-        <v>6983790</v>
+        <v>6984011</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128826022</v>
+        <v>128824312</v>
       </c>
       <c r="B10" t="n">
-        <v>80146</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,13 +1566,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536178</v>
+        <v>536282</v>
       </c>
       <c r="R10" t="n">
-        <v>6983822</v>
+        <v>6983998</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128824312</v>
+        <v>128826022</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>80146</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536282</v>
+        <v>536178</v>
       </c>
       <c r="R11" t="n">
-        <v>6983998</v>
+        <v>6983822</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128826828</v>
+        <v>128826455</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,13 +1887,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536179</v>
+        <v>536225</v>
       </c>
       <c r="R13" t="n">
-        <v>6983752</v>
+        <v>6983790</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128826455</v>
+        <v>128826828</v>
       </c>
       <c r="B14" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536225</v>
+        <v>536179</v>
       </c>
       <c r="R14" t="n">
-        <v>6983790</v>
+        <v>6983752</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128826139</v>
+        <v>128826203</v>
       </c>
       <c r="B16" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536203</v>
+        <v>536194</v>
       </c>
       <c r="R16" t="n">
-        <v>6983808</v>
+        <v>6983796</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,7 +2280,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128825959</v>
+        <v>128826139</v>
       </c>
       <c r="B17" t="n">
         <v>80146</v>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536251</v>
+        <v>536203</v>
       </c>
       <c r="R17" t="n">
-        <v>6983900</v>
+        <v>6983808</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128826203</v>
+        <v>128825959</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2398,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536194</v>
+        <v>536251</v>
       </c>
       <c r="R18" t="n">
-        <v>6983796</v>
+        <v>6983900</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 40482-2021 artfynd.xlsx
+++ b/artfynd/A 40482-2021 artfynd.xlsx
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128826455</v>
+        <v>128826828</v>
       </c>
       <c r="B13" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,13 +1887,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536225</v>
+        <v>536179</v>
       </c>
       <c r="R13" t="n">
-        <v>6983790</v>
+        <v>6983752</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128826828</v>
+        <v>128826455</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536179</v>
+        <v>536225</v>
       </c>
       <c r="R14" t="n">
-        <v>6983752</v>
+        <v>6983790</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 40482-2021 artfynd.xlsx
+++ b/artfynd/A 40482-2021 artfynd.xlsx
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128824312</v>
+        <v>128826022</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>80146</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,13 +1566,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536282</v>
+        <v>536178</v>
       </c>
       <c r="R10" t="n">
-        <v>6983998</v>
+        <v>6983822</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128826022</v>
+        <v>128824312</v>
       </c>
       <c r="B11" t="n">
-        <v>80146</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536178</v>
+        <v>536282</v>
       </c>
       <c r="R11" t="n">
-        <v>6983822</v>
+        <v>6983998</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128826203</v>
+        <v>128826139</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536194</v>
+        <v>536203</v>
       </c>
       <c r="R16" t="n">
-        <v>6983796</v>
+        <v>6983808</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,7 +2280,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128826139</v>
+        <v>128825959</v>
       </c>
       <c r="B17" t="n">
         <v>80146</v>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536203</v>
+        <v>536251</v>
       </c>
       <c r="R17" t="n">
-        <v>6983808</v>
+        <v>6983900</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128825959</v>
+        <v>128826203</v>
       </c>
       <c r="B18" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2398,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536251</v>
+        <v>536194</v>
       </c>
       <c r="R18" t="n">
-        <v>6983900</v>
+        <v>6983796</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2601,32 +2601,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128827111</v>
+        <v>128827232</v>
       </c>
       <c r="B20" t="n">
-        <v>80174</v>
+        <v>57887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,13 +2636,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>536165</v>
+        <v>536125</v>
       </c>
       <c r="R20" t="n">
-        <v>6983788</v>
+        <v>6983800</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,32 +2708,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128827232</v>
+        <v>128827111</v>
       </c>
       <c r="B21" t="n">
-        <v>57887</v>
+        <v>80174</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,13 +2743,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>536125</v>
+        <v>536165</v>
       </c>
       <c r="R21" t="n">
-        <v>6983800</v>
+        <v>6983788</v>
       </c>
       <c r="S21" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 40482-2021 artfynd.xlsx
+++ b/artfynd/A 40482-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128826263</v>
+        <v>128824312</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,13 +1352,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536215</v>
+        <v>536282</v>
       </c>
       <c r="R8" t="n">
-        <v>6983790</v>
+        <v>6983998</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128827725</v>
+        <v>128826263</v>
       </c>
       <c r="B9" t="n">
         <v>57727</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536141</v>
+        <v>536215</v>
       </c>
       <c r="R9" t="n">
-        <v>6984011</v>
+        <v>6983790</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128826022</v>
+        <v>128827725</v>
       </c>
       <c r="B10" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536178</v>
+        <v>536141</v>
       </c>
       <c r="R10" t="n">
-        <v>6983822</v>
+        <v>6984011</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128824312</v>
+        <v>128826022</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>80146</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536282</v>
+        <v>536178</v>
       </c>
       <c r="R11" t="n">
-        <v>6983998</v>
+        <v>6983822</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2601,32 +2601,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128827232</v>
+        <v>128827111</v>
       </c>
       <c r="B20" t="n">
-        <v>57887</v>
+        <v>80174</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,13 +2636,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>536125</v>
+        <v>536165</v>
       </c>
       <c r="R20" t="n">
-        <v>6983800</v>
+        <v>6983788</v>
       </c>
       <c r="S20" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,32 +2708,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128827111</v>
+        <v>128827232</v>
       </c>
       <c r="B21" t="n">
-        <v>80174</v>
+        <v>57887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,13 +2743,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>536165</v>
+        <v>536125</v>
       </c>
       <c r="R21" t="n">
-        <v>6983788</v>
+        <v>6983800</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3245,6 +3245,327 @@
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129405479</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>536222</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6984002</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129405903</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>536213</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6983974</v>
+      </c>
+      <c r="S27" t="n">
+        <v>20</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129406557</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>536295</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6983976</v>
+      </c>
+      <c r="S28" t="n">
+        <v>20</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40482-2021 artfynd.xlsx
+++ b/artfynd/A 40482-2021 artfynd.xlsx
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128824312</v>
+        <v>128826022</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>80146</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,13 +1352,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536282</v>
+        <v>536178</v>
       </c>
       <c r="R8" t="n">
-        <v>6983998</v>
+        <v>6983822</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128826263</v>
+        <v>128824312</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,13 +1459,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536215</v>
+        <v>536282</v>
       </c>
       <c r="R9" t="n">
-        <v>6983790</v>
+        <v>6983998</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128827725</v>
+        <v>128826263</v>
       </c>
       <c r="B10" t="n">
         <v>57727</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536141</v>
+        <v>536215</v>
       </c>
       <c r="R10" t="n">
-        <v>6984011</v>
+        <v>6983790</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128826022</v>
+        <v>128827725</v>
       </c>
       <c r="B11" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536178</v>
+        <v>536141</v>
       </c>
       <c r="R11" t="n">
-        <v>6983822</v>
+        <v>6984011</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128826828</v>
+        <v>128826455</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,13 +1887,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536179</v>
+        <v>536225</v>
       </c>
       <c r="R13" t="n">
-        <v>6983752</v>
+        <v>6983790</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128826455</v>
+        <v>128826828</v>
       </c>
       <c r="B14" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536225</v>
+        <v>536179</v>
       </c>
       <c r="R14" t="n">
-        <v>6983790</v>
+        <v>6983752</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128826139</v>
+        <v>128826203</v>
       </c>
       <c r="B16" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536203</v>
+        <v>536194</v>
       </c>
       <c r="R16" t="n">
-        <v>6983808</v>
+        <v>6983796</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,7 +2280,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128825959</v>
+        <v>128826139</v>
       </c>
       <c r="B17" t="n">
         <v>80146</v>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536251</v>
+        <v>536203</v>
       </c>
       <c r="R17" t="n">
-        <v>6983900</v>
+        <v>6983808</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128826203</v>
+        <v>128825959</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2398,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536194</v>
+        <v>536251</v>
       </c>
       <c r="R18" t="n">
-        <v>6983796</v>
+        <v>6983900</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 40482-2021 artfynd.xlsx
+++ b/artfynd/A 40482-2021 artfynd.xlsx
@@ -3139,7 +3139,7 @@
         <v>128826667</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>129405479</v>
       </c>
       <c r="B26" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>129405903</v>
       </c>
       <c r="B27" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>129406557</v>
       </c>
       <c r="B28" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 40482-2021 artfynd.xlsx
+++ b/artfynd/A 40482-2021 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>128825631</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>128826263</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>128827725</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>128826828</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>128826101</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>128826203</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>128825735</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>128827644</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>128826667</v>
       </c>
       <c r="B25" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>129405479</v>
       </c>
       <c r="B26" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>129405903</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>129406557</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 40482-2021 artfynd.xlsx
+++ b/artfynd/A 40482-2021 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>128825631</v>
       </c>
       <c r="B6" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>128826263</v>
       </c>
       <c r="B10" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>128827725</v>
       </c>
       <c r="B11" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>128826828</v>
       </c>
       <c r="B14" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>128826101</v>
       </c>
       <c r="B15" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>128826203</v>
       </c>
       <c r="B16" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>128825735</v>
       </c>
       <c r="B19" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>128827644</v>
       </c>
       <c r="B24" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>128826667</v>
       </c>
       <c r="B25" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>129405479</v>
       </c>
       <c r="B26" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>129405903</v>
       </c>
       <c r="B27" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>129406557</v>
       </c>
       <c r="B28" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 40482-2021 artfynd.xlsx
+++ b/artfynd/A 40482-2021 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>128825631</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>128826263</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>128827725</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>128826828</v>
       </c>
       <c r="B14" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>128826101</v>
       </c>
       <c r="B15" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>128826203</v>
       </c>
       <c r="B16" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>128825735</v>
       </c>
       <c r="B19" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>128827644</v>
       </c>
       <c r="B24" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>128826667</v>
       </c>
       <c r="B25" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 40482-2021 artfynd.xlsx
+++ b/artfynd/A 40482-2021 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>128825631</v>
       </c>
       <c r="B6" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>128826263</v>
       </c>
       <c r="B10" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>128827725</v>
       </c>
       <c r="B11" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>128826828</v>
       </c>
       <c r="B14" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>128826101</v>
       </c>
       <c r="B15" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>128826203</v>
       </c>
       <c r="B16" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>128825735</v>
       </c>
       <c r="B19" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>128827644</v>
       </c>
       <c r="B24" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>128826667</v>
       </c>
       <c r="B25" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
